--- a/waiver_forms/028_paintball_waiver_form--waiver_forms.xlsx
+++ b/waiver_forms/028_paintball_waiver_form--waiver_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -811,8 +811,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="46" customWidth="1" min="2" max="2"/>
-    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="33" customWidth="1" min="2" max="2"/>
+    <col width="33" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -840,12 +840,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'phone_number:_123-123-1234'}</t>
+          <t>phone_number:_123-123-1234</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Phone Number: 123-123-1234'}</t>
+          <t>Phone Number: 123-123-1234</t>
         </is>
       </c>
     </row>
@@ -857,12 +857,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'email_address:_test@example.com'}</t>
+          <t>email_address:_test@example.com</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Email Address: test@example.com'}</t>
+          <t>Email Address: test@example.com</t>
         </is>
       </c>
     </row>
@@ -874,12 +874,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'123_main_st.'}</t>
+          <t>123_main_st.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': '123 Main St.'}</t>
+          <t>123 Main St.</t>
         </is>
       </c>
     </row>
@@ -891,12 +891,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'456_elm_st.'}</t>
+          <t>456_elm_st.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': '456 Elm St.'}</t>
+          <t>456 Elm St.</t>
         </is>
       </c>
     </row>
@@ -908,12 +908,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'789_oak_st.'}</t>
+          <t>789_oak_st.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': '789 Oak St.'}</t>
+          <t>789 Oak St.</t>
         </is>
       </c>
     </row>
@@ -925,12 +925,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'diabetes'}</t>
+          <t>diabetes</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Diabetes'}</t>
+          <t>Diabetes</t>
         </is>
       </c>
     </row>
@@ -942,12 +942,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'hypertension'}</t>
+          <t>hypertension</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Hypertension'}</t>
+          <t>Hypertension</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'heart_disease'}</t>
+          <t>heart_disease</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Heart Disease'}</t>
+          <t>Heart Disease</t>
         </is>
       </c>
     </row>
@@ -976,12 +976,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'ambulance'}</t>
+          <t>ambulance</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Ambulance'}</t>
+          <t>Ambulance</t>
         </is>
       </c>
     </row>
@@ -993,12 +993,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'fire_department'}</t>
+          <t>fire_department</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Fire Department'}</t>
+          <t>Fire Department</t>
         </is>
       </c>
     </row>
@@ -1010,12 +1010,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'police_department'}</t>
+          <t>police_department</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Police Department'}</t>
+          <t>Police Department</t>
         </is>
       </c>
     </row>
@@ -1061,12 +1061,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'i_agree'}</t>
+          <t>i_agree</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'I agree'}</t>
+          <t>I agree</t>
         </is>
       </c>
     </row>
@@ -1078,12 +1078,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'i_do_not_agree'}</t>
+          <t>i_do_not_agree</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'I do not agree'}</t>
+          <t>I do not agree</t>
         </is>
       </c>
     </row>
@@ -1095,12 +1095,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'ambulance_2'}</t>
+          <t>ambulance_2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Ambulance 2'}</t>
+          <t>Ambulance 2</t>
         </is>
       </c>
     </row>
@@ -1112,12 +1112,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'fire_department_2'}</t>
+          <t>fire_department_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Fire Department 2'}</t>
+          <t>Fire Department 2</t>
         </is>
       </c>
     </row>
@@ -1129,12 +1129,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'police_department_2'}</t>
+          <t>police_department_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Police Department 2'}</t>
+          <t>Police Department 2</t>
         </is>
       </c>
     </row>
